--- a/static/data/source/unemployment_rate.xlsx
+++ b/static/data/source/unemployment_rate.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aboddupalli\Box\TIS\TPC\CENTER\SLFI\Interactive Data Tools\SEM\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM BLS Update\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0111CA05-E4E9-4712-A34E-2A2E4F383C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7513F722-0DF5-4544-A45D-91C41B78AC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TABLE_1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="653">
   <si>
     <t>Geography</t>
   </si>
@@ -1822,6 +1822,9 @@
     <t>11/01/2025</t>
   </si>
   <si>
+    <t>12/01/2025</t>
+  </si>
+  <si>
     <t>United States</t>
   </si>
   <si>
@@ -2309,10 +2312,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:WB56"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A4:WC56"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="4" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -4113,10 +4116,13 @@
       <c r="WB4" t="s">
         <v>599</v>
       </c>
+      <c r="WC4" t="s">
+        <v>600</v>
+      </c>
     </row>
-    <row r="5" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B5">
         <v>7.9</v>
@@ -5769,7 +5775,7 @@
         <v>4.5</v>
       </c>
       <c r="UF5">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="UG5">
         <v>3.9</v>
@@ -5778,7 +5784,7 @@
         <v>4</v>
       </c>
       <c r="UI5">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="UJ5">
         <v>3.7</v>
@@ -5835,7 +5841,7 @@
         <v>3.7</v>
       </c>
       <c r="VB5">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="VC5">
         <v>3.9</v>
@@ -5859,7 +5865,7 @@
         <v>3.9</v>
       </c>
       <c r="VJ5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="VK5">
         <v>4.0999999999999996</v>
@@ -5886,7 +5892,7 @@
         <v>4</v>
       </c>
       <c r="VS5">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="VT5">
         <v>4.2</v>
@@ -5895,13 +5901,13 @@
         <v>4.2</v>
       </c>
       <c r="VV5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="VW5">
         <v>4.0999999999999996</v>
       </c>
       <c r="VX5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="VY5">
         <v>4.3</v>
@@ -5913,12 +5919,15 @@
         <v>0</v>
       </c>
       <c r="WB5">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
+      </c>
+      <c r="WC5">
+        <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B6">
         <v>6.7</v>
@@ -7717,10 +7726,13 @@
       <c r="WB6">
         <v>2.7</v>
       </c>
+      <c r="WC6">
+        <v>2.7</v>
+      </c>
     </row>
-    <row r="7" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B7">
         <v>7.1</v>
@@ -9519,10 +9531,13 @@
       <c r="WB7">
         <v>4.7</v>
       </c>
+      <c r="WC7">
+        <v>4.8</v>
+      </c>
     </row>
-    <row r="8" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B8">
         <v>10.199999999999999</v>
@@ -11321,10 +11336,13 @@
       <c r="WB8">
         <v>4.3</v>
       </c>
+      <c r="WC8">
+        <v>4.3</v>
+      </c>
     </row>
-    <row r="9" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B9">
         <v>7.3</v>
@@ -13123,10 +13141,13 @@
       <c r="WB9">
         <v>4.0999999999999996</v>
       </c>
+      <c r="WC9">
+        <v>4.2</v>
+      </c>
     </row>
-    <row r="10" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B10">
         <v>9.1999999999999993</v>
@@ -14923,12 +14944,15 @@
         <v>0</v>
       </c>
       <c r="WB10">
+        <v>5.6</v>
+      </c>
+      <c r="WC10">
         <v>5.5</v>
       </c>
     </row>
-    <row r="11" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B11">
         <v>5.8</v>
@@ -16727,10 +16751,13 @@
       <c r="WB11">
         <v>3.9</v>
       </c>
+      <c r="WC11">
+        <v>3.8</v>
+      </c>
     </row>
-    <row r="12" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B12">
         <v>9.6999999999999993</v>
@@ -18529,10 +18556,13 @@
       <c r="WB12">
         <v>4</v>
       </c>
+      <c r="WC12">
+        <v>4.2</v>
+      </c>
     </row>
-    <row r="13" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B13">
         <v>8</v>
@@ -20331,10 +20361,13 @@
       <c r="WB13">
         <v>4.9000000000000004</v>
       </c>
+      <c r="WC13">
+        <v>5.2</v>
+      </c>
     </row>
-    <row r="14" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B14">
         <v>8.8000000000000007</v>
@@ -22133,10 +22166,13 @@
       <c r="WB14">
         <v>6.5</v>
       </c>
+      <c r="WC14">
+        <v>6.7</v>
+      </c>
     </row>
-    <row r="15" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B15">
         <v>9.6</v>
@@ -23935,10 +23971,13 @@
       <c r="WB15">
         <v>4.2</v>
       </c>
+      <c r="WC15">
+        <v>4.3</v>
+      </c>
     </row>
-    <row r="16" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B16">
         <v>8.4</v>
@@ -25737,10 +25776,13 @@
       <c r="WB16">
         <v>3.5</v>
       </c>
+      <c r="WC16">
+        <v>3.6</v>
+      </c>
     </row>
-    <row r="17" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B17">
         <v>9.6</v>
@@ -27539,10 +27581,13 @@
       <c r="WB17">
         <v>2.2000000000000002</v>
       </c>
+      <c r="WC17">
+        <v>2.2000000000000002</v>
+      </c>
     </row>
-    <row r="18" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B18">
         <v>5.6</v>
@@ -29341,10 +29386,13 @@
       <c r="WB18">
         <v>3.7</v>
       </c>
+      <c r="WC18">
+        <v>3.6</v>
+      </c>
     </row>
-    <row r="19" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B19">
         <v>6.6</v>
@@ -31143,10 +31191,13 @@
       <c r="WB19">
         <v>4.4000000000000004</v>
       </c>
+      <c r="WC19">
+        <v>4.5999999999999996</v>
+      </c>
     </row>
-    <row r="20" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B20">
         <v>6.6</v>
@@ -32945,10 +32996,13 @@
       <c r="WB20">
         <v>3.7</v>
       </c>
+      <c r="WC20">
+        <v>3.5</v>
+      </c>
     </row>
-    <row r="21" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B21">
         <v>4.4000000000000004</v>
@@ -34747,10 +34801,13 @@
       <c r="WB21">
         <v>3.5</v>
       </c>
+      <c r="WC21">
+        <v>3.5</v>
+      </c>
     </row>
-    <row r="22" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B22">
         <v>4.2</v>
@@ -36549,10 +36606,13 @@
       <c r="WB22">
         <v>3.8</v>
       </c>
+      <c r="WC22">
+        <v>3.8</v>
+      </c>
     </row>
-    <row r="23" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B23">
         <v>5.6</v>
@@ -38351,10 +38411,13 @@
       <c r="WB23">
         <v>4.7</v>
       </c>
+      <c r="WC23">
+        <v>4.5</v>
+      </c>
     </row>
-    <row r="24" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B24">
         <v>6.3</v>
@@ -40153,10 +40216,13 @@
       <c r="WB24">
         <v>4.3</v>
       </c>
+      <c r="WC24">
+        <v>4.2</v>
+      </c>
     </row>
-    <row r="25" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B25">
         <v>8.6999999999999993</v>
@@ -41955,10 +42021,13 @@
       <c r="WB25">
         <v>3.2</v>
       </c>
+      <c r="WC25">
+        <v>3.2</v>
+      </c>
     </row>
-    <row r="26" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B26">
         <v>6.5</v>
@@ -43757,10 +43826,13 @@
       <c r="WB26">
         <v>4.2</v>
       </c>
+      <c r="WC26">
+        <v>4.2</v>
+      </c>
     </row>
-    <row r="27" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B27">
         <v>10.6</v>
@@ -45559,10 +45631,13 @@
       <c r="WB27">
         <v>4.7</v>
       </c>
+      <c r="WC27">
+        <v>4.8</v>
+      </c>
     </row>
-    <row r="28" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B28">
         <v>9.9</v>
@@ -47361,10 +47436,13 @@
       <c r="WB28">
         <v>5</v>
       </c>
+      <c r="WC28">
+        <v>5</v>
+      </c>
     </row>
-    <row r="29" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B29">
         <v>5.9</v>
@@ -49163,10 +49241,13 @@
       <c r="WB29">
         <v>4</v>
       </c>
+      <c r="WC29">
+        <v>4.0999999999999996</v>
+      </c>
     </row>
-    <row r="30" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B30">
         <v>6.6</v>
@@ -50965,10 +51046,13 @@
       <c r="WB30">
         <v>3.8</v>
       </c>
+      <c r="WC30">
+        <v>3.7</v>
+      </c>
     </row>
-    <row r="31" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -52767,10 +52851,13 @@
       <c r="WB31">
         <v>4</v>
       </c>
+      <c r="WC31">
+        <v>3.9</v>
+      </c>
     </row>
-    <row r="32" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B32">
         <v>5.9</v>
@@ -54569,10 +54656,13 @@
       <c r="WB32">
         <v>3.3</v>
       </c>
+      <c r="WC32">
+        <v>3.4</v>
+      </c>
     </row>
-    <row r="33" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B33">
         <v>3.2</v>
@@ -56371,10 +56461,13 @@
       <c r="WB33">
         <v>3</v>
       </c>
+      <c r="WC33">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B34">
         <v>9.1999999999999993</v>
@@ -58173,10 +58266,13 @@
       <c r="WB34">
         <v>5.2</v>
       </c>
+      <c r="WC34">
+        <v>5.2</v>
+      </c>
     </row>
-    <row r="35" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B35">
         <v>6.5</v>
@@ -59975,10 +60071,13 @@
       <c r="WB35">
         <v>3</v>
       </c>
+      <c r="WC35">
+        <v>3.1</v>
+      </c>
     </row>
-    <row r="36" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B36">
         <v>10.199999999999999</v>
@@ -61777,10 +61876,13 @@
       <c r="WB36">
         <v>5.4</v>
       </c>
+      <c r="WC36">
+        <v>5.4</v>
+      </c>
     </row>
-    <row r="37" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B37">
         <v>8.6</v>
@@ -63579,10 +63681,13 @@
       <c r="WB37">
         <v>4.2</v>
       </c>
+      <c r="WC37">
+        <v>4.3</v>
+      </c>
     </row>
-    <row r="38" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B38">
         <v>10.3</v>
@@ -65381,10 +65486,13 @@
       <c r="WB38">
         <v>4.5</v>
       </c>
+      <c r="WC38">
+        <v>4.5999999999999996</v>
+      </c>
     </row>
-    <row r="39" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B39">
         <v>6.5</v>
@@ -67181,12 +67289,15 @@
         <v>0</v>
       </c>
       <c r="WB39">
-        <v>3.8</v>
+        <v>3.9</v>
+      </c>
+      <c r="WC39">
+        <v>3.9</v>
       </c>
     </row>
-    <row r="40" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B40">
         <v>3.5</v>
@@ -68985,10 +69096,13 @@
       <c r="WB40">
         <v>2.6</v>
       </c>
+      <c r="WC40">
+        <v>2.6</v>
+      </c>
     </row>
-    <row r="41" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B41">
         <v>8.1</v>
@@ -70787,10 +70901,13 @@
       <c r="WB41">
         <v>4.5</v>
       </c>
+      <c r="WC41">
+        <v>4.5</v>
+      </c>
     </row>
-    <row r="42" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B42">
         <v>5.8</v>
@@ -72589,10 +72706,13 @@
       <c r="WB42">
         <v>3.5</v>
       </c>
+      <c r="WC42">
+        <v>3.6</v>
+      </c>
     </row>
-    <row r="43" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B43">
         <v>9.5</v>
@@ -74391,10 +74511,13 @@
       <c r="WB43">
         <v>5.2</v>
       </c>
+      <c r="WC43">
+        <v>5.2</v>
+      </c>
     </row>
-    <row r="44" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B44">
         <v>8.1</v>
@@ -76193,10 +76316,13 @@
       <c r="WB44">
         <v>4.2</v>
       </c>
+      <c r="WC44">
+        <v>4.2</v>
+      </c>
     </row>
-    <row r="45" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B45">
         <v>7.7</v>
@@ -77995,10 +78121,13 @@
       <c r="WB45">
         <v>4.3</v>
       </c>
+      <c r="WC45">
+        <v>4.3</v>
+      </c>
     </row>
-    <row r="46" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B46">
         <v>7.3</v>
@@ -79797,10 +79926,13 @@
       <c r="WB46">
         <v>4.5999999999999996</v>
       </c>
+      <c r="WC46">
+        <v>4.8</v>
+      </c>
     </row>
-    <row r="47" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B47">
         <v>3.3</v>
@@ -81599,10 +81731,13 @@
       <c r="WB47">
         <v>2.1</v>
       </c>
+      <c r="WC47">
+        <v>2.2000000000000002</v>
+      </c>
     </row>
-    <row r="48" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B48">
         <v>6</v>
@@ -83401,10 +83536,13 @@
       <c r="WB48">
         <v>3.6</v>
       </c>
+      <c r="WC48">
+        <v>3.6</v>
+      </c>
     </row>
-    <row r="49" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B49">
         <v>5.8</v>
@@ -85203,10 +85341,13 @@
       <c r="WB49">
         <v>4.2</v>
       </c>
+      <c r="WC49">
+        <v>4.3</v>
+      </c>
     </row>
-    <row r="50" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B50">
         <v>5.8</v>
@@ -87005,10 +87146,13 @@
       <c r="WB50">
         <v>3.6</v>
       </c>
+      <c r="WC50">
+        <v>3.6</v>
+      </c>
     </row>
-    <row r="51" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B51">
         <v>8.5</v>
@@ -88807,10 +88951,13 @@
       <c r="WB51">
         <v>2.6</v>
       </c>
+      <c r="WC51">
+        <v>2.6</v>
+      </c>
     </row>
-    <row r="52" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B52">
         <v>6</v>
@@ -90609,10 +90756,13 @@
       <c r="WB52">
         <v>3.5</v>
       </c>
+      <c r="WC52">
+        <v>3.6</v>
+      </c>
     </row>
-    <row r="53" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B53">
         <v>8.5</v>
@@ -92411,10 +92561,13 @@
       <c r="WB53">
         <v>4.5999999999999996</v>
       </c>
+      <c r="WC53">
+        <v>4.7</v>
+      </c>
     </row>
-    <row r="54" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B54">
         <v>7.4</v>
@@ -94213,10 +94366,13 @@
       <c r="WB54">
         <v>4.4000000000000004</v>
       </c>
+      <c r="WC54">
+        <v>4.5999999999999996</v>
+      </c>
     </row>
-    <row r="55" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B55">
         <v>5.8</v>
@@ -96015,10 +96171,13 @@
       <c r="WB55">
         <v>3.1</v>
       </c>
+      <c r="WC55">
+        <v>3.1</v>
+      </c>
     </row>
-    <row r="56" spans="1:600" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:601" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B56">
         <v>4.0999999999999996</v>
@@ -97815,6 +97974,9 @@
         <v>0</v>
       </c>
       <c r="WB56">
+        <v>3.4</v>
+      </c>
+      <c r="WC56">
         <v>3.4</v>
       </c>
     </row>

--- a/static/data/source/unemployment_rate.xlsx
+++ b/static/data/source/unemployment_rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\TPC\Scratch\Garriga\D drive transfer\SEM BLS Update\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM BLS Update\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FF0462-FF77-4D01-8F2F-5B9F6E086A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8361097B-6944-4F84-81F2-D913443FBD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="16200" windowHeight="9270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TABLE_1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
   <si>
     <t>Geography</t>
   </si>
@@ -1828,6 +1828,9 @@
     <t>01/01/2026</t>
   </si>
   <si>
+    <t>02/01/2026</t>
+  </si>
+  <si>
     <t>United States</t>
   </si>
   <si>
@@ -2315,10 +2318,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:WD56"/>
+  <dimension ref="A4:WE56"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -4125,10 +4128,13 @@
       <c r="WD4" t="s">
         <v>601</v>
       </c>
+      <c r="WE4" t="s">
+        <v>602</v>
+      </c>
     </row>
-    <row r="5" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B5">
         <v>7.9</v>
@@ -5933,10 +5939,13 @@
       <c r="WD5">
         <v>4.3</v>
       </c>
+      <c r="WE5">
+        <v>4.4000000000000004</v>
+      </c>
     </row>
-    <row r="6" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B6">
         <v>6.7</v>
@@ -7741,10 +7750,13 @@
       <c r="WD6">
         <v>2.7</v>
       </c>
+      <c r="WE6">
+        <v>2.7</v>
+      </c>
     </row>
-    <row r="7" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B7">
         <v>7.1</v>
@@ -9549,10 +9561,13 @@
       <c r="WD7">
         <v>4.8</v>
       </c>
+      <c r="WE7">
+        <v>4.7</v>
+      </c>
     </row>
-    <row r="8" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B8">
         <v>10.199999999999999</v>
@@ -11357,10 +11372,13 @@
       <c r="WD8">
         <v>4.5</v>
       </c>
+      <c r="WE8">
+        <v>4.5999999999999996</v>
+      </c>
     </row>
-    <row r="9" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B9">
         <v>7.3</v>
@@ -13165,10 +13183,13 @@
       <c r="WD9">
         <v>4.4000000000000004</v>
       </c>
+      <c r="WE9">
+        <v>4.4000000000000004</v>
+      </c>
     </row>
-    <row r="10" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B10">
         <v>9.1999999999999993</v>
@@ -14973,10 +14994,13 @@
       <c r="WD10">
         <v>5.4</v>
       </c>
+      <c r="WE10">
+        <v>5.4</v>
+      </c>
     </row>
-    <row r="11" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B11">
         <v>5.8</v>
@@ -16781,10 +16805,13 @@
       <c r="WD11">
         <v>3.9</v>
       </c>
+      <c r="WE11">
+        <v>3.9</v>
+      </c>
     </row>
-    <row r="12" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B12">
         <v>9.6999999999999993</v>
@@ -18589,10 +18616,13 @@
       <c r="WD12">
         <v>4.5</v>
       </c>
+      <c r="WE12">
+        <v>4.7</v>
+      </c>
     </row>
-    <row r="13" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B13">
         <v>8</v>
@@ -20397,10 +20427,13 @@
       <c r="WD13">
         <v>5.4</v>
       </c>
+      <c r="WE13">
+        <v>5.4</v>
+      </c>
     </row>
-    <row r="14" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B14">
         <v>8.8000000000000007</v>
@@ -22205,10 +22238,13 @@
       <c r="WD14">
         <v>6.7</v>
       </c>
+      <c r="WE14">
+        <v>6.5</v>
+      </c>
     </row>
-    <row r="15" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B15">
         <v>9.6</v>
@@ -24013,10 +24049,13 @@
       <c r="WD15">
         <v>4.5</v>
       </c>
+      <c r="WE15">
+        <v>4.5999999999999996</v>
+      </c>
     </row>
-    <row r="16" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B16">
         <v>8.4</v>
@@ -25821,10 +25860,13 @@
       <c r="WD16">
         <v>3.5</v>
       </c>
+      <c r="WE16">
+        <v>3.6</v>
+      </c>
     </row>
-    <row r="17" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B17">
         <v>9.6</v>
@@ -27629,10 +27671,13 @@
       <c r="WD17">
         <v>2.2000000000000002</v>
       </c>
+      <c r="WE17">
+        <v>2.2999999999999998</v>
+      </c>
     </row>
-    <row r="18" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B18">
         <v>5.6</v>
@@ -29437,10 +29482,13 @@
       <c r="WD18">
         <v>3.7</v>
       </c>
+      <c r="WE18">
+        <v>3.7</v>
+      </c>
     </row>
-    <row r="19" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B19">
         <v>6.6</v>
@@ -31245,10 +31293,13 @@
       <c r="WD19">
         <v>4.9000000000000004</v>
       </c>
+      <c r="WE19">
+        <v>5</v>
+      </c>
     </row>
-    <row r="20" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B20">
         <v>6.6</v>
@@ -33053,10 +33104,13 @@
       <c r="WD20">
         <v>3.4</v>
       </c>
+      <c r="WE20">
+        <v>3.3</v>
+      </c>
     </row>
-    <row r="21" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B21">
         <v>4.4000000000000004</v>
@@ -34861,10 +34915,13 @@
       <c r="WD21">
         <v>3.4</v>
       </c>
+      <c r="WE21">
+        <v>3.4</v>
+      </c>
     </row>
-    <row r="22" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B22">
         <v>4.2</v>
@@ -36669,10 +36726,13 @@
       <c r="WD22">
         <v>3.9</v>
       </c>
+      <c r="WE22">
+        <v>3.9</v>
+      </c>
     </row>
-    <row r="23" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B23">
         <v>5.6</v>
@@ -38477,10 +38537,13 @@
       <c r="WD23">
         <v>4.3</v>
       </c>
+      <c r="WE23">
+        <v>4.2</v>
+      </c>
     </row>
-    <row r="24" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B24">
         <v>6.3</v>
@@ -40285,10 +40348,13 @@
       <c r="WD24">
         <v>4.3</v>
       </c>
+      <c r="WE24">
+        <v>4.3</v>
+      </c>
     </row>
-    <row r="25" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B25">
         <v>8.6999999999999993</v>
@@ -42093,10 +42159,13 @@
       <c r="WD25">
         <v>3.3</v>
       </c>
+      <c r="WE25">
+        <v>3.2</v>
+      </c>
     </row>
-    <row r="26" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B26">
         <v>6.5</v>
@@ -43901,10 +43970,13 @@
       <c r="WD26">
         <v>4.3</v>
       </c>
+      <c r="WE26">
+        <v>4.3</v>
+      </c>
     </row>
-    <row r="27" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B27">
         <v>10.6</v>
@@ -45709,10 +45781,13 @@
       <c r="WD27">
         <v>4.7</v>
       </c>
+      <c r="WE27">
+        <v>4.8</v>
+      </c>
     </row>
-    <row r="28" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B28">
         <v>9.9</v>
@@ -47517,10 +47592,13 @@
       <c r="WD28">
         <v>5</v>
       </c>
+      <c r="WE28">
+        <v>5</v>
+      </c>
     </row>
-    <row r="29" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B29">
         <v>5.9</v>
@@ -49325,10 +49403,13 @@
       <c r="WD29">
         <v>4.4000000000000004</v>
       </c>
+      <c r="WE29">
+        <v>4.5</v>
+      </c>
     </row>
-    <row r="30" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B30">
         <v>6.6</v>
@@ -51133,10 +51214,13 @@
       <c r="WD30">
         <v>3.6</v>
       </c>
+      <c r="WE30">
+        <v>3.7</v>
+      </c>
     </row>
-    <row r="31" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -52941,10 +53025,13 @@
       <c r="WD31">
         <v>3.9</v>
       </c>
+      <c r="WE31">
+        <v>3.9</v>
+      </c>
     </row>
-    <row r="32" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B32">
         <v>5.9</v>
@@ -54749,10 +54836,13 @@
       <c r="WD32">
         <v>3.6</v>
       </c>
+      <c r="WE32">
+        <v>3.6</v>
+      </c>
     </row>
-    <row r="33" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B33">
         <v>3.2</v>
@@ -56557,10 +56647,13 @@
       <c r="WD33">
         <v>3</v>
       </c>
+      <c r="WE33">
+        <v>3.1</v>
+      </c>
     </row>
-    <row r="34" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B34">
         <v>9.1999999999999993</v>
@@ -58365,10 +58458,13 @@
       <c r="WD34">
         <v>5.3</v>
       </c>
+      <c r="WE34">
+        <v>5.3</v>
+      </c>
     </row>
-    <row r="35" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B35">
         <v>6.5</v>
@@ -60173,10 +60269,13 @@
       <c r="WD35">
         <v>3.2</v>
       </c>
+      <c r="WE35">
+        <v>3.2</v>
+      </c>
     </row>
-    <row r="36" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B36">
         <v>10.199999999999999</v>
@@ -61981,10 +62080,13 @@
       <c r="WD36">
         <v>5.2</v>
       </c>
+      <c r="WE36">
+        <v>5.0999999999999996</v>
+      </c>
     </row>
-    <row r="37" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B37">
         <v>8.6</v>
@@ -63789,10 +63891,13 @@
       <c r="WD37">
         <v>4.5</v>
       </c>
+      <c r="WE37">
+        <v>4.7</v>
+      </c>
     </row>
-    <row r="38" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B38">
         <v>10.3</v>
@@ -65597,10 +65702,13 @@
       <c r="WD38">
         <v>4.5999999999999996</v>
       </c>
+      <c r="WE38">
+        <v>4.5999999999999996</v>
+      </c>
     </row>
-    <row r="39" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B39">
         <v>6.5</v>
@@ -67405,10 +67513,13 @@
       <c r="WD39">
         <v>3.8</v>
       </c>
+      <c r="WE39">
+        <v>3.8</v>
+      </c>
     </row>
-    <row r="40" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B40">
         <v>3.5</v>
@@ -69213,10 +69324,13 @@
       <c r="WD40">
         <v>2.6</v>
       </c>
+      <c r="WE40">
+        <v>2.6</v>
+      </c>
     </row>
-    <row r="41" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B41">
         <v>8.1</v>
@@ -71021,10 +71135,13 @@
       <c r="WD41">
         <v>4.3</v>
       </c>
+      <c r="WE41">
+        <v>4.2</v>
+      </c>
     </row>
-    <row r="42" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B42">
         <v>5.8</v>
@@ -72829,10 +72946,13 @@
       <c r="WD42">
         <v>3.9</v>
       </c>
+      <c r="WE42">
+        <v>3.9</v>
+      </c>
     </row>
-    <row r="43" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B43">
         <v>9.5</v>
@@ -74637,10 +74757,13 @@
       <c r="WD43">
         <v>5.2</v>
       </c>
+      <c r="WE43">
+        <v>5.2</v>
+      </c>
     </row>
-    <row r="44" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B44">
         <v>8.1</v>
@@ -76445,10 +76568,13 @@
       <c r="WD44">
         <v>4.3</v>
       </c>
+      <c r="WE44">
+        <v>4.2</v>
+      </c>
     </row>
-    <row r="45" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B45">
         <v>7.7</v>
@@ -78253,10 +78379,13 @@
       <c r="WD45">
         <v>4.5</v>
       </c>
+      <c r="WE45">
+        <v>4.5999999999999996</v>
+      </c>
     </row>
-    <row r="46" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B46">
         <v>7.3</v>
@@ -80061,10 +80190,13 @@
       <c r="WD46">
         <v>4.9000000000000004</v>
       </c>
+      <c r="WE46">
+        <v>5</v>
+      </c>
     </row>
-    <row r="47" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B47">
         <v>3.3</v>
@@ -81869,10 +82001,13 @@
       <c r="WD47">
         <v>2.2000000000000002</v>
       </c>
+      <c r="WE47">
+        <v>2.2999999999999998</v>
+      </c>
     </row>
-    <row r="48" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B48">
         <v>6</v>
@@ -83677,10 +83812,13 @@
       <c r="WD48">
         <v>3.5</v>
       </c>
+      <c r="WE48">
+        <v>3.6</v>
+      </c>
     </row>
-    <row r="49" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B49">
         <v>5.8</v>
@@ -85485,10 +85623,13 @@
       <c r="WD49">
         <v>4.3</v>
       </c>
+      <c r="WE49">
+        <v>4.3</v>
+      </c>
     </row>
-    <row r="50" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B50">
         <v>5.8</v>
@@ -87293,10 +87434,13 @@
       <c r="WD50">
         <v>3.8</v>
       </c>
+      <c r="WE50">
+        <v>3.8</v>
+      </c>
     </row>
-    <row r="51" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B51">
         <v>8.5</v>
@@ -89101,10 +89245,13 @@
       <c r="WD51">
         <v>2.7</v>
       </c>
+      <c r="WE51">
+        <v>2.6</v>
+      </c>
     </row>
-    <row r="52" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B52">
         <v>6</v>
@@ -90909,10 +91056,13 @@
       <c r="WD52">
         <v>3.7</v>
       </c>
+      <c r="WE52">
+        <v>3.7</v>
+      </c>
     </row>
-    <row r="53" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B53">
         <v>8.5</v>
@@ -92717,10 +92867,13 @@
       <c r="WD53">
         <v>5</v>
       </c>
+      <c r="WE53">
+        <v>5.0999999999999996</v>
+      </c>
     </row>
-    <row r="54" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B54">
         <v>7.4</v>
@@ -94525,10 +94678,13 @@
       <c r="WD54">
         <v>4.5999999999999996</v>
       </c>
+      <c r="WE54">
+        <v>4.7</v>
+      </c>
     </row>
-    <row r="55" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B55">
         <v>5.8</v>
@@ -96333,10 +96489,13 @@
       <c r="WD55">
         <v>3.3</v>
       </c>
+      <c r="WE55">
+        <v>3.4</v>
+      </c>
     </row>
-    <row r="56" spans="1:602" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:603" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B56">
         <v>4.0999999999999996</v>
@@ -98139,6 +98298,9 @@
         <v>3.5</v>
       </c>
       <c r="WD56">
+        <v>3.6</v>
+      </c>
+      <c r="WE56">
         <v>3.6</v>
       </c>
     </row>

--- a/static/data/source/unemployment_rate.xlsx
+++ b/static/data/source/unemployment_rate.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A4:WF56"/>
+  <dimension ref="A4:WG56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4">
@@ -3393,6 +3393,11 @@
           <t>03/01/2026</t>
         </is>
       </c>
+      <c r="WG4" t="inlineStr">
+        <is>
+          <t>04/01/2026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5209,6 +5214,9 @@
       <c r="WF5">
         <v>4.3</v>
       </c>
+      <c r="WG5">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7025,6 +7033,9 @@
       <c r="WF6">
         <v>2.7</v>
       </c>
+      <c r="WG6">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8841,6 +8852,9 @@
       <c r="WF7">
         <v>4.7</v>
       </c>
+      <c r="WG7">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10657,6 +10671,9 @@
       <c r="WF8">
         <v>4.7</v>
       </c>
+      <c r="WG8">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12473,6 +12490,9 @@
       <c r="WF9">
         <v>4.3</v>
       </c>
+      <c r="WG9">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14289,6 +14309,9 @@
       <c r="WF10">
         <v>5.3</v>
       </c>
+      <c r="WG10">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16105,6 +16128,9 @@
       <c r="WF11">
         <v>3.9</v>
       </c>
+      <c r="WG11">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17921,6 +17947,9 @@
       <c r="WF12">
         <v>4.8</v>
       </c>
+      <c r="WG12">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19737,6 +19766,9 @@
       <c r="WF13">
         <v>5.4</v>
       </c>
+      <c r="WG13">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21553,6 +21585,9 @@
       <c r="WF14">
         <v>6.3</v>
       </c>
+      <c r="WG14">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23369,6 +23404,9 @@
       <c r="WF15">
         <v>4.7</v>
       </c>
+      <c r="WG15">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25185,6 +25223,9 @@
       <c r="WF16">
         <v>3.5</v>
       </c>
+      <c r="WG16">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27001,6 +27042,9 @@
       <c r="WF17">
         <v>2.4</v>
       </c>
+      <c r="WG17">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -28817,6 +28861,9 @@
       <c r="WF18">
         <v>3.6</v>
       </c>
+      <c r="WG18">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30633,6 +30680,9 @@
       <c r="WF19">
         <v>5.1</v>
       </c>
+      <c r="WG19">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -32449,6 +32499,9 @@
       <c r="WF20">
         <v>3.3</v>
       </c>
+      <c r="WG20">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -34265,6 +34318,9 @@
       <c r="WF21">
         <v>3.3</v>
       </c>
+      <c r="WG21">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -36081,6 +36137,9 @@
       <c r="WF22">
         <v>3.9</v>
       </c>
+      <c r="WG22">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -37897,6 +37956,9 @@
       <c r="WF23">
         <v>4.2</v>
       </c>
+      <c r="WG23">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -39713,6 +39775,9 @@
       <c r="WF24">
         <v>4.4</v>
       </c>
+      <c r="WG24">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -41529,6 +41594,9 @@
       <c r="WF25">
         <v>3.2</v>
       </c>
+      <c r="WG25">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -43345,6 +43413,9 @@
       <c r="WF26">
         <v>4.3</v>
       </c>
+      <c r="WG26">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -45161,6 +45232,9 @@
       <c r="WF27">
         <v>4.7</v>
       </c>
+      <c r="WG27">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -46977,6 +47051,9 @@
       <c r="WF28">
         <v>5</v>
       </c>
+      <c r="WG28">
+        <v>5</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -48793,6 +48870,9 @@
       <c r="WF29">
         <v>4.5</v>
       </c>
+      <c r="WG29">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -50609,6 +50689,9 @@
       <c r="WF30">
         <v>3.8</v>
       </c>
+      <c r="WG30">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -52425,6 +52508,9 @@
       <c r="WF31">
         <v>3.9</v>
       </c>
+      <c r="WG31">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -54241,6 +54327,9 @@
       <c r="WF32">
         <v>3.6</v>
       </c>
+      <c r="WG32">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -56057,6 +56146,9 @@
       <c r="WF33">
         <v>3.1</v>
       </c>
+      <c r="WG33">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -57873,6 +57965,9 @@
       <c r="WF34">
         <v>5.3</v>
       </c>
+      <c r="WG34">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -59689,6 +59784,9 @@
       <c r="WF35">
         <v>3.1</v>
       </c>
+      <c r="WG35">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -61505,6 +61603,9 @@
       <c r="WF36">
         <v>4.9</v>
       </c>
+      <c r="WG36">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -63321,6 +63422,9 @@
       <c r="WF37">
         <v>4.8</v>
       </c>
+      <c r="WG37">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -65137,6 +65241,9 @@
       <c r="WF38">
         <v>4.6</v>
       </c>
+      <c r="WG38">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -66953,6 +67060,9 @@
       <c r="WF39">
         <v>3.7</v>
       </c>
+      <c r="WG39">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -68769,6 +68879,9 @@
       <c r="WF40">
         <v>2.5</v>
       </c>
+      <c r="WG40">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -70585,6 +70698,9 @@
       <c r="WF41">
         <v>4.1</v>
       </c>
+      <c r="WG41">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -72401,6 +72517,9 @@
       <c r="WF42">
         <v>3.9</v>
       </c>
+      <c r="WG42">
+        <v>4</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -74217,6 +74336,9 @@
       <c r="WF43">
         <v>5.2</v>
       </c>
+      <c r="WG43">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -76033,6 +76155,9 @@
       <c r="WF44">
         <v>4.2</v>
       </c>
+      <c r="WG44">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -77849,6 +77974,9 @@
       <c r="WF45">
         <v>4.7</v>
       </c>
+      <c r="WG45">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -79665,6 +79793,9 @@
       <c r="WF46">
         <v>4.9</v>
       </c>
+      <c r="WG46">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -81481,6 +81612,9 @@
       <c r="WF47">
         <v>2.3</v>
       </c>
+      <c r="WG47">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -83297,6 +83431,9 @@
       <c r="WF48">
         <v>3.6</v>
       </c>
+      <c r="WG48">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -85113,6 +85250,9 @@
       <c r="WF49">
         <v>4.3</v>
       </c>
+      <c r="WG49">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -86929,6 +87069,9 @@
       <c r="WF50">
         <v>3.8</v>
       </c>
+      <c r="WG50">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -88745,6 +88888,9 @@
       <c r="WF51">
         <v>2.6</v>
       </c>
+      <c r="WG51">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -90561,6 +90707,9 @@
       <c r="WF52">
         <v>3.8</v>
       </c>
+      <c r="WG52">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -92377,6 +92526,9 @@
       <c r="WF53">
         <v>5.1</v>
       </c>
+      <c r="WG53">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -94193,6 +94345,9 @@
       <c r="WF54">
         <v>4.5</v>
       </c>
+      <c r="WG54">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -96009,6 +96164,9 @@
       <c r="WF55">
         <v>3.5</v>
       </c>
+      <c r="WG55">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -97824,6 +97982,9 @@
       </c>
       <c r="WF56">
         <v>3.6</v>
+      </c>
+      <c r="WG56">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>

--- a/static/data/source/unemployment_rate.xlsx
+++ b/static/data/source/unemployment_rate.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A4:WG56"/>
+  <dimension ref="A4:WH56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4">
@@ -3398,6 +3398,11 @@
           <t>04/01/2026</t>
         </is>
       </c>
+      <c r="WH4" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5217,6 +5222,9 @@
       <c r="WG5">
         <v>4.3</v>
       </c>
+      <c r="WH5">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7036,6 +7044,9 @@
       <c r="WG6">
         <v>2.8</v>
       </c>
+      <c r="WH6">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8853,7 +8864,10 @@
         <v>4.7</v>
       </c>
       <c r="WG7">
-        <v>4.7</v>
+        <v>4.6</v>
+      </c>
+      <c r="WH7">
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
@@ -10674,6 +10688,9 @@
       <c r="WG8">
         <v>4.7</v>
       </c>
+      <c r="WH8">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12493,6 +12510,9 @@
       <c r="WG9">
         <v>4.3</v>
       </c>
+      <c r="WH9">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14312,6 +14332,9 @@
       <c r="WG10">
         <v>5.3</v>
       </c>
+      <c r="WH10">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16131,6 +16154,9 @@
       <c r="WG11">
         <v>3.9</v>
       </c>
+      <c r="WH11">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17950,6 +17976,9 @@
       <c r="WG12">
         <v>5</v>
       </c>
+      <c r="WH12">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19769,6 +19798,9 @@
       <c r="WG13">
         <v>5.3</v>
       </c>
+      <c r="WH13">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21588,6 +21620,9 @@
       <c r="WG14">
         <v>6.2</v>
       </c>
+      <c r="WH14">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23407,6 +23442,9 @@
       <c r="WG15">
         <v>4.8</v>
       </c>
+      <c r="WH15">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25226,6 +25264,9 @@
       <c r="WG16">
         <v>3.5</v>
       </c>
+      <c r="WH16">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27043,6 +27084,9 @@
         <v>2.4</v>
       </c>
       <c r="WG17">
+        <v>2.4</v>
+      </c>
+      <c r="WH17">
         <v>2.5</v>
       </c>
     </row>
@@ -28864,6 +28908,9 @@
       <c r="WG18">
         <v>3.6</v>
       </c>
+      <c r="WH18">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30683,6 +30730,9 @@
       <c r="WG19">
         <v>5.1</v>
       </c>
+      <c r="WH19">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -32500,7 +32550,10 @@
         <v>3.3</v>
       </c>
       <c r="WG20">
-        <v>3.2</v>
+        <v>3.3</v>
+      </c>
+      <c r="WH20">
+        <v>3.3</v>
       </c>
     </row>
     <row r="21">
@@ -34321,6 +34374,9 @@
       <c r="WG21">
         <v>3.3</v>
       </c>
+      <c r="WH21">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -36140,6 +36196,9 @@
       <c r="WG22">
         <v>3.9</v>
       </c>
+      <c r="WH22">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -37959,6 +38018,9 @@
       <c r="WG23">
         <v>4.3</v>
       </c>
+      <c r="WH23">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -39778,6 +39840,9 @@
       <c r="WG24">
         <v>4.4</v>
       </c>
+      <c r="WH24">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -41597,6 +41662,9 @@
       <c r="WG25">
         <v>3.1</v>
       </c>
+      <c r="WH25">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -43416,6 +43484,9 @@
       <c r="WG26">
         <v>4.4</v>
       </c>
+      <c r="WH26">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -45235,6 +45306,9 @@
       <c r="WG27">
         <v>4.7</v>
       </c>
+      <c r="WH27">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -47054,6 +47128,9 @@
       <c r="WG28">
         <v>5</v>
       </c>
+      <c r="WH28">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -48873,6 +48950,9 @@
       <c r="WG29">
         <v>4.5</v>
       </c>
+      <c r="WH29">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -50692,6 +50772,9 @@
       <c r="WG30">
         <v>3.8</v>
       </c>
+      <c r="WH30">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -52511,6 +52594,9 @@
       <c r="WG31">
         <v>3.8</v>
       </c>
+      <c r="WH31">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -54330,6 +54416,9 @@
       <c r="WG32">
         <v>3.5</v>
       </c>
+      <c r="WH32">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -56149,6 +56238,9 @@
       <c r="WG33">
         <v>3</v>
       </c>
+      <c r="WH33">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -57968,6 +58060,9 @@
       <c r="WG34">
         <v>5.3</v>
       </c>
+      <c r="WH34">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -59787,6 +59882,9 @@
       <c r="WG35">
         <v>3.1</v>
       </c>
+      <c r="WH35">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -61606,6 +61704,9 @@
       <c r="WG36">
         <v>4.8</v>
       </c>
+      <c r="WH36">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -63425,6 +63526,9 @@
       <c r="WG37">
         <v>4.9</v>
       </c>
+      <c r="WH37">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -65244,6 +65348,9 @@
       <c r="WG38">
         <v>4.6</v>
       </c>
+      <c r="WH38">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -67063,6 +67170,9 @@
       <c r="WG39">
         <v>3.7</v>
       </c>
+      <c r="WH39">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -68882,6 +68992,9 @@
       <c r="WG40">
         <v>2.4</v>
       </c>
+      <c r="WH40">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -70701,6 +70814,9 @@
       <c r="WG41">
         <v>3.9</v>
       </c>
+      <c r="WH41">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -72520,6 +72636,9 @@
       <c r="WG42">
         <v>4</v>
       </c>
+      <c r="WH42">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -74339,6 +74458,9 @@
       <c r="WG43">
         <v>5.2</v>
       </c>
+      <c r="WH43">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -76158,6 +76280,9 @@
       <c r="WG44">
         <v>4.2</v>
       </c>
+      <c r="WH44">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -77977,6 +78102,9 @@
       <c r="WG45">
         <v>4.5</v>
       </c>
+      <c r="WH45">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -79796,6 +79924,9 @@
       <c r="WG46">
         <v>4.8</v>
       </c>
+      <c r="WH46">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -81615,6 +81746,9 @@
       <c r="WG47">
         <v>2.2</v>
       </c>
+      <c r="WH47">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -83434,6 +83568,9 @@
       <c r="WG48">
         <v>3.6</v>
       </c>
+      <c r="WH48">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -85253,6 +85390,9 @@
       <c r="WG49">
         <v>4.3</v>
       </c>
+      <c r="WH49">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -87072,6 +87212,9 @@
       <c r="WG50">
         <v>3.8</v>
       </c>
+      <c r="WH50">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -88891,6 +89034,9 @@
       <c r="WG51">
         <v>2.6</v>
       </c>
+      <c r="WH51">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -90710,6 +90856,9 @@
       <c r="WG52">
         <v>3.8</v>
       </c>
+      <c r="WH52">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -92529,6 +92678,9 @@
       <c r="WG53">
         <v>5.2</v>
       </c>
+      <c r="WH53">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -94348,6 +94500,9 @@
       <c r="WG54">
         <v>4.4</v>
       </c>
+      <c r="WH54">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -96167,6 +96322,9 @@
       <c r="WG55">
         <v>3.5</v>
       </c>
+      <c r="WH55">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -97985,6 +98143,9 @@
       </c>
       <c r="WG56">
         <v>3.5</v>
+      </c>
+      <c r="WH56">
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>

--- a/static/data/source/unemployment_rate.xlsx
+++ b/static/data/source/unemployment_rate.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A4:WH56"/>
+  <dimension ref="A4:WI56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4">
@@ -3403,6 +3403,11 @@
           <t>05/01/2026</t>
         </is>
       </c>
+      <c r="WI4" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5225,6 +5230,9 @@
       <c r="WH5">
         <v>4.3</v>
       </c>
+      <c r="WI5">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7047,6 +7055,9 @@
       <c r="WH6">
         <v>3</v>
       </c>
+      <c r="WI6">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8869,6 +8880,9 @@
       <c r="WH7">
         <v>4.6</v>
       </c>
+      <c r="WI7">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10691,6 +10705,9 @@
       <c r="WH8">
         <v>4.8</v>
       </c>
+      <c r="WI8">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12513,6 +12530,9 @@
       <c r="WH9">
         <v>4.2</v>
       </c>
+      <c r="WI9">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14335,6 +14355,9 @@
       <c r="WH10">
         <v>5.3</v>
       </c>
+      <c r="WI10">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16157,6 +16180,9 @@
       <c r="WH11">
         <v>3.9</v>
       </c>
+      <c r="WI11">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17979,6 +18005,9 @@
       <c r="WH12">
         <v>5.1</v>
       </c>
+      <c r="WI12">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19801,6 +19830,9 @@
       <c r="WH13">
         <v>5.1</v>
       </c>
+      <c r="WI13">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21623,6 +21655,9 @@
       <c r="WH14">
         <v>6.1</v>
       </c>
+      <c r="WI14">
+        <v>6</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23445,6 +23480,9 @@
       <c r="WH15">
         <v>4.8</v>
       </c>
+      <c r="WI15">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25267,6 +25305,9 @@
       <c r="WH16">
         <v>3.4</v>
       </c>
+      <c r="WI16">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27089,6 +27130,9 @@
       <c r="WH17">
         <v>2.5</v>
       </c>
+      <c r="WI17">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -28911,6 +28955,9 @@
       <c r="WH18">
         <v>3.7</v>
       </c>
+      <c r="WI18">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30733,6 +30780,9 @@
       <c r="WH19">
         <v>5.1</v>
       </c>
+      <c r="WI19">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -32555,6 +32605,9 @@
       <c r="WH20">
         <v>3.3</v>
       </c>
+      <c r="WI20">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -34377,6 +34430,9 @@
       <c r="WH21">
         <v>3.2</v>
       </c>
+      <c r="WI21">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -36199,6 +36255,9 @@
       <c r="WH22">
         <v>3.8</v>
       </c>
+      <c r="WI22">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -38021,6 +38080,9 @@
       <c r="WH23">
         <v>4.5</v>
       </c>
+      <c r="WI23">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -39843,6 +39905,9 @@
       <c r="WH24">
         <v>4.5</v>
       </c>
+      <c r="WI24">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -41665,6 +41730,9 @@
       <c r="WH25">
         <v>3.1</v>
       </c>
+      <c r="WI25">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -43487,6 +43555,9 @@
       <c r="WH26">
         <v>4.4</v>
       </c>
+      <c r="WI26">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -45309,6 +45380,9 @@
       <c r="WH27">
         <v>4.5</v>
       </c>
+      <c r="WI27">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -47131,6 +47205,9 @@
       <c r="WH28">
         <v>5.1</v>
       </c>
+      <c r="WI28">
+        <v>5</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -48953,6 +49030,9 @@
       <c r="WH29">
         <v>4.4</v>
       </c>
+      <c r="WI29">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -50775,6 +50855,9 @@
       <c r="WH30">
         <v>3.8</v>
       </c>
+      <c r="WI30">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -52597,6 +52680,9 @@
       <c r="WH31">
         <v>3.8</v>
       </c>
+      <c r="WI31">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -54419,6 +54505,9 @@
       <c r="WH32">
         <v>3.4</v>
       </c>
+      <c r="WI32">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -56241,6 +56330,9 @@
       <c r="WH33">
         <v>3</v>
       </c>
+      <c r="WI33">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -58063,6 +58155,9 @@
       <c r="WH34">
         <v>5.2</v>
       </c>
+      <c r="WI34">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -59885,6 +59980,9 @@
       <c r="WH35">
         <v>3</v>
       </c>
+      <c r="WI35">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -61707,6 +61805,9 @@
       <c r="WH36">
         <v>4.7</v>
       </c>
+      <c r="WI36">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -63529,6 +63630,9 @@
       <c r="WH37">
         <v>4.9</v>
       </c>
+      <c r="WI37">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -65351,6 +65455,9 @@
       <c r="WH38">
         <v>4.6</v>
       </c>
+      <c r="WI38">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -67173,6 +67280,9 @@
       <c r="WH39">
         <v>3.7</v>
       </c>
+      <c r="WI39">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -68995,6 +69105,9 @@
       <c r="WH40">
         <v>2.4</v>
       </c>
+      <c r="WI40">
+        <v>2.3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -70817,6 +70930,9 @@
       <c r="WH41">
         <v>3.7</v>
       </c>
+      <c r="WI41">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -72639,6 +72755,9 @@
       <c r="WH42">
         <v>4.1</v>
       </c>
+      <c r="WI42">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -74461,6 +74580,9 @@
       <c r="WH43">
         <v>5.2</v>
       </c>
+      <c r="WI43">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -76283,6 +76405,9 @@
       <c r="WH44">
         <v>4.2</v>
       </c>
+      <c r="WI44">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -78105,6 +78230,9 @@
       <c r="WH45">
         <v>4.3</v>
       </c>
+      <c r="WI45">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -79927,6 +80055,9 @@
       <c r="WH46">
         <v>4.6</v>
       </c>
+      <c r="WI46">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -81749,6 +81880,9 @@
       <c r="WH47">
         <v>2.1</v>
       </c>
+      <c r="WI47">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -83571,6 +83705,9 @@
       <c r="WH48">
         <v>3.6</v>
       </c>
+      <c r="WI48">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -85393,6 +85530,9 @@
       <c r="WH49">
         <v>4.3</v>
       </c>
+      <c r="WI49">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -87215,6 +87355,9 @@
       <c r="WH50">
         <v>3.7</v>
       </c>
+      <c r="WI50">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -89037,6 +89180,9 @@
       <c r="WH51">
         <v>2.6</v>
       </c>
+      <c r="WI51">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -90859,6 +91005,9 @@
       <c r="WH52">
         <v>3.8</v>
       </c>
+      <c r="WI52">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -92681,6 +92830,9 @@
       <c r="WH53">
         <v>5.2</v>
       </c>
+      <c r="WI53">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -94503,6 +94655,9 @@
       <c r="WH54">
         <v>4.3</v>
       </c>
+      <c r="WI54">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -96325,6 +96480,9 @@
       <c r="WH55">
         <v>3.4</v>
       </c>
+      <c r="WI55">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -98146,6 +98304,9 @@
       </c>
       <c r="WH56">
         <v>3.4</v>
+      </c>
+      <c r="WI56">
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>

--- a/static/data/source/unemployment_rate.xlsx
+++ b/static/data/source/unemployment_rate.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A4:WI56"/>
+  <dimension ref="A4:WJ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4">
@@ -3408,6 +3408,11 @@
           <t>06/01/2026</t>
         </is>
       </c>
+      <c r="WJ4" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5233,6 +5238,9 @@
       <c r="WI5">
         <v>4.2</v>
       </c>
+      <c r="WJ5">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7058,6 +7066,9 @@
       <c r="WI6">
         <v>3.2</v>
       </c>
+      <c r="WJ6">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8883,6 +8894,9 @@
       <c r="WI7">
         <v>4.4</v>
       </c>
+      <c r="WJ7">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10708,6 +10722,9 @@
       <c r="WI8">
         <v>4.9</v>
       </c>
+      <c r="WJ8">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12533,6 +12550,9 @@
       <c r="WI9">
         <v>4.1</v>
       </c>
+      <c r="WJ9">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14358,6 +14378,9 @@
       <c r="WI10">
         <v>5.2</v>
       </c>
+      <c r="WJ10">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16183,6 +16206,9 @@
       <c r="WI11">
         <v>3.9</v>
       </c>
+      <c r="WJ11">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18008,6 +18034,9 @@
       <c r="WI12">
         <v>5.2</v>
       </c>
+      <c r="WJ12">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19833,6 +19862,9 @@
       <c r="WI13">
         <v>4.9</v>
       </c>
+      <c r="WJ13">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -21658,6 +21690,9 @@
       <c r="WI14">
         <v>6</v>
       </c>
+      <c r="WJ14">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23483,6 +23518,9 @@
       <c r="WI15">
         <v>4.7</v>
       </c>
+      <c r="WJ15">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25308,6 +25346,9 @@
       <c r="WI16">
         <v>3.4</v>
       </c>
+      <c r="WJ16">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27133,6 +27174,9 @@
       <c r="WI17">
         <v>2.6</v>
       </c>
+      <c r="WJ17">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -28958,6 +29002,9 @@
       <c r="WI18">
         <v>3.7</v>
       </c>
+      <c r="WJ18">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -30783,6 +30830,9 @@
       <c r="WI19">
         <v>5.1</v>
       </c>
+      <c r="WJ19">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -32608,6 +32658,9 @@
       <c r="WI20">
         <v>3.3</v>
       </c>
+      <c r="WJ20">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -34433,6 +34486,9 @@
       <c r="WI21">
         <v>3.2</v>
       </c>
+      <c r="WJ21">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -36258,6 +36314,9 @@
       <c r="WI22">
         <v>3.8</v>
       </c>
+      <c r="WJ22">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -38083,6 +38142,9 @@
       <c r="WI23">
         <v>4.7</v>
       </c>
+      <c r="WJ23">
+        <v>4.7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -39908,6 +39970,9 @@
       <c r="WI24">
         <v>4.4</v>
       </c>
+      <c r="WJ24">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -41733,6 +41798,9 @@
       <c r="WI25">
         <v>3.1</v>
       </c>
+      <c r="WJ25">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -43558,6 +43626,9 @@
       <c r="WI26">
         <v>4.3</v>
       </c>
+      <c r="WJ26">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -45383,6 +45454,9 @@
       <c r="WI27">
         <v>4.4</v>
       </c>
+      <c r="WJ27">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -47208,6 +47282,9 @@
       <c r="WI28">
         <v>5</v>
       </c>
+      <c r="WJ28">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -49033,6 +49110,9 @@
       <c r="WI29">
         <v>4.4</v>
       </c>
+      <c r="WJ29">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -50858,6 +50938,9 @@
       <c r="WI30">
         <v>3.8</v>
       </c>
+      <c r="WJ30">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -52683,6 +52766,9 @@
       <c r="WI31">
         <v>3.7</v>
       </c>
+      <c r="WJ31">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -54508,6 +54594,9 @@
       <c r="WI32">
         <v>3.3</v>
       </c>
+      <c r="WJ32">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -56333,6 +56422,9 @@
       <c r="WI33">
         <v>2.9</v>
       </c>
+      <c r="WJ33">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -58158,6 +58250,9 @@
       <c r="WI34">
         <v>5.1</v>
       </c>
+      <c r="WJ34">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -59983,6 +60078,9 @@
       <c r="WI35">
         <v>2.9</v>
       </c>
+      <c r="WJ35">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -61808,6 +61906,9 @@
       <c r="WI36">
         <v>4.5</v>
       </c>
+      <c r="WJ36">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -63633,6 +63734,9 @@
       <c r="WI37">
         <v>4.8</v>
       </c>
+      <c r="WJ37">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -65458,6 +65562,9 @@
       <c r="WI38">
         <v>4.6</v>
       </c>
+      <c r="WJ38">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -67283,6 +67390,9 @@
       <c r="WI39">
         <v>3.6</v>
       </c>
+      <c r="WJ39">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -69108,6 +69218,9 @@
       <c r="WI40">
         <v>2.3</v>
       </c>
+      <c r="WJ40">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -70933,6 +71046,9 @@
       <c r="WI41">
         <v>3.6</v>
       </c>
+      <c r="WJ41">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -72758,6 +72874,9 @@
       <c r="WI42">
         <v>4.2</v>
       </c>
+      <c r="WJ42">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -74583,6 +74702,9 @@
       <c r="WI43">
         <v>5.2</v>
       </c>
+      <c r="WJ43">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -76408,6 +76530,9 @@
       <c r="WI44">
         <v>4.1</v>
       </c>
+      <c r="WJ44">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -78233,6 +78358,9 @@
       <c r="WI45">
         <v>4.1</v>
       </c>
+      <c r="WJ45">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -80058,6 +80186,9 @@
       <c r="WI46">
         <v>4.4</v>
       </c>
+      <c r="WJ46">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -81883,6 +82014,9 @@
       <c r="WI47">
         <v>2</v>
       </c>
+      <c r="WJ47">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -83708,6 +83842,9 @@
       <c r="WI48">
         <v>3.5</v>
       </c>
+      <c r="WJ48">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -85533,6 +85670,9 @@
       <c r="WI49">
         <v>4.4</v>
       </c>
+      <c r="WJ49">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -87358,6 +87498,9 @@
       <c r="WI50">
         <v>3.6</v>
       </c>
+      <c r="WJ50">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -89183,6 +89326,9 @@
       <c r="WI51">
         <v>2.6</v>
       </c>
+      <c r="WJ51">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -91006,6 +91152,9 @@
         <v>3.8</v>
       </c>
       <c r="WI52">
+        <v>3.8</v>
+      </c>
+      <c r="WJ52">
         <v>3.7</v>
       </c>
     </row>
@@ -92833,6 +92982,9 @@
       <c r="WI53">
         <v>5.2</v>
       </c>
+      <c r="WJ53">
+        <v>5</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -94658,6 +94810,9 @@
       <c r="WI54">
         <v>4.2</v>
       </c>
+      <c r="WJ54">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -96483,6 +96638,9 @@
       <c r="WI55">
         <v>3.3</v>
       </c>
+      <c r="WJ55">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -98307,6 +98465,9 @@
       </c>
       <c r="WI56">
         <v>3.2</v>
+      </c>
+      <c r="WJ56">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
